--- a/data/Creatine/lanhers2015/lanhers2015_creatine_leg_press_strength.xlsx
+++ b/data/Creatine/lanhers2015/lanhers2015_creatine_leg_press_strength.xlsx
@@ -149,7 +149,7 @@
     <t>notes</t>
   </si>
   <si>
-    <t>n not available so smd used</t>
+    <t>n not available, d used</t>
   </si>
 </sst>
 </file>
